--- a/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,77 +453,189 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AszX60rp</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>hQiNHHd2</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jix3jCxF</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>C6QBlj7R</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h6Py6Kcj</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>dbI3Q902</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CKCtVmJf</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WdOu5vDd</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>zkH7PTF8</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>KCHNTNkc</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>UPVAOmVE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CKCtVmJf</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>b3GRSs53</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+          <t>8GUEN7pL</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>tS5WR1K9</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+          <t>juKJMRaR</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h29zRLZF</t>
+          <t>Usy7kWiL</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -526,19 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WWvwigh8</t>
+          <t xml:space="preserve">chapman a 
+  usa </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>022mBmSn</t>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>QF7rPa4S</t>
+          <t>lSHwpAFr</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -546,19 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UFWZoX9L</t>
+          <t xml:space="preserve">villarreal a 
+  usa </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>86yPt28f</t>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>nP8vQukM</t>
+          <t>MNAkH5Nl</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -566,19 +695,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sd7snoa0</t>
+          <t xml:space="preserve">freemon j 
+  usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WSL0wFD4</t>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>69kBKJCq</t>
+          <t>S0BoIo8r</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -586,19 +721,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2PIEeC7j</t>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>rXawJi8t</t>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vNmJIcsd</t>
+          <t>0E9gGPxe</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -606,19 +747,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t xml:space="preserve">pekmic i 
+  usa </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>rXawJi8t</t>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>bFuhdIb3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>MHXbihN8</t>
+          <t>Ik4bFqh1</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -626,19 +773,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sd7snoa0</t>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>86yPt28f</t>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>p0lFJwSk</t>
+          <t>dt32E377</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -646,12 +799,70 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>2PIEeC7j</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>rXawJi8t</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>WSL0wFD4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>vqenBDBt</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fierro r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>n9nYS6gm</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>SWX9C8ZI</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hQiNHHd2</t>
+          <t>hIoLKAg0</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapman a 
+          <t xml:space="preserve">szpala l 
   usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UFWZoX9L</t>
+          <t>zoZ995af</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UL7r7duf</t>
+          <t>tOpyQa24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>C6QBlj7R</t>
+          <t>KEflYcbt</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>K4FYmLD9</t>
+          <t>rXawJi8t</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>WWvwigh8</t>
+          <t>2PIEeC7j</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dbI3Q902</t>
+          <t>EyfhXHDn</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
+          <t xml:space="preserve">mendoza r 
   usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KtuTuMN0</t>
+          <t>rJ9D8rzj</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CKCtVmJf</t>
+          <t>txm4BKVR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>zkH7PTF8</t>
+          <t>SvbdWyTh</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>UFWZoX9L</t>
+          <t>6LuGZiZI</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>WWvwigh8</t>
+          <t>nJ01AhXP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UPVAOmVE</t>
+          <t>AoWGqXpJ</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
+          <t xml:space="preserve">villarreal a 
   usa </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6gpXy3vi</t>
+          <t>UL7r7duf</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CKCtVmJf</t>
+          <t>86yPt28f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>8GUEN7pL</t>
+          <t>trWntSE7</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,278 +591,18 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
-  usa </t>
+          <t xml:space="preserve">montero r 
+  cos </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>K4zRMgTN</t>
+          <t>KtuTuMN0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6LuGZiZI</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>juKJMRaR</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>6BusaLE3</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>zoZ995af</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Usy7kWiL</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chapman a 
-  usa </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Sd7snoa0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>UL7r7duf</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>lSHwpAFr</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">villarreal a 
-  usa </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Sd7snoa0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>xA45kovo</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>MNAkH5Nl</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">freemon j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6BusaLE3</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>022mBmSn</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>S0BoIo8r</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jBBpU7Y0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>dp6AQn9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>0E9gGPxe</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pekmic i 
-  usa </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
           <t>lAVQ9RGh</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>bFuhdIb3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ik4bFqh1</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2PIEeC7j</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>zoZ995af</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dt32E377</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vazquez r 
-  usa </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2PIEeC7j</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>WSL0wFD4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>vqenBDBt</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fierro r 
-  usa </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>jBBpU7Y0</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>n9nYS6gm</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>SWX9C8ZI</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chapman a 
-  usa </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>tOpyQa24</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>UL7r7duf</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,12 +459,7 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">szpala l 
-  usa </t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>zoZ995af</t>
@@ -485,12 +480,7 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>rXawJi8t</t>
@@ -511,12 +501,7 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>rJ9D8rzj</t>
@@ -537,12 +522,7 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">de oliveira m 
-  usa </t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>6LuGZiZI</t>
@@ -563,12 +543,7 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">villarreal a 
-  usa </t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>UL7r7duf</t>
@@ -589,12 +564,7 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">montero r 
-  cos </t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>KtuTuMN0</t>
@@ -603,6 +573,344 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>lAVQ9RGh</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>A3m1Vera</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>63fk89be</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8lOY3V6E</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ITj9TZCB</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>lfn5UFc5</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>dKkDSgSH</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vquIRDsO</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bazakos f 
+  usa </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>jDDw3kMK</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xUcLQXdU</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EkZQoHSu</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bazakos f 
+  usa </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>htYUpyrn</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>WSL0wFD4</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AHSZqech</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">szpala l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>l8RwqFCb</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villarreal a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>WSL0wFD4</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>foKU4Bi8</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,133 +453,163 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hIoLKAg0</t>
+          <t>A3m1Vera</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>zoZ995af</t>
+          <t>022mBmSn</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t>63fk89be</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KEflYcbt</t>
+          <t>8lOY3V6E</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>rXawJi8t</t>
+          <t>roEEsq76</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2PIEeC7j</t>
+          <t>l6eEjGlO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EyfhXHDn</t>
+          <t>ITj9TZCB</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>rJ9D8rzj</t>
+          <t>6LuGZiZI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>txm4BKVR</t>
+          <t>dp6AQn9c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SvbdWyTh</t>
+          <t>lfn5UFc5</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6LuGZiZI</t>
+          <t>roEEsq76</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>nJ01AhXP</t>
+          <t>tOpyQa24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AoWGqXpJ</t>
+          <t>dKkDSgSH</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>UL7r7duf</t>
+          <t>6LuGZiZI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>86yPt28f</t>
+          <t>6BusaLE3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>trWntSE7</t>
+          <t>vquIRDsO</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KtuTuMN0</t>
+          <t>K4zRMgTN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>lAVQ9RGh</t>
+          <t>WSL0wFD4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>A3m1Vera</t>
+          <t>jDDw3kMK</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -587,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivas v 
+          <t xml:space="preserve">allatin m 
   usa </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>022mBmSn</t>
+          <t>xA45kovo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>63fk89be</t>
+          <t>Sd7snoa0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
+          <t>xUcLQXdU</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -613,25 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
+          <t xml:space="preserve">touchan r 
   usa </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>roEEsq76</t>
+          <t>6LuGZiZI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>l6eEjGlO</t>
+          <t>jBBpU7Y0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
+          <t>EkZQoHSu</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -639,25 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
+          <t xml:space="preserve">bazakos f 
   usa </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>xA45kovo</t>
+          <t>86yPt28f</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>dp6AQn9c</t>
+          <t>GzULyFoh</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>htYUpyrn</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -665,25 +695,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
+          <t xml:space="preserve">demianchuk s 
   usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>roEEsq76</t>
+          <t>GzULyFoh</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>dp6AQn9c</t>
+          <t>UFWZoX9L</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>AHSZqech</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -691,25 +721,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
+          <t xml:space="preserve">szpala l 
   usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6LuGZiZI</t>
+          <t>WWvwigh8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6BusaLE3</t>
+          <t>tOpyQa24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vquIRDsO</t>
+          <t>l8RwqFCb</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -717,25 +747,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">bazakos f 
+          <t xml:space="preserve">gonzales g 
   usa </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>K4zRMgTN</t>
+          <t>WSL0wFD4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GzULyFoh</t>
+          <t>UL7r7duf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>foKU4Bi8</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -743,25 +773,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">allatin m 
+          <t xml:space="preserve">demianchuk s 
   usa </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>xA45kovo</t>
+          <t>Sd7snoa0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sd7snoa0</t>
+          <t>UFWZoX9L</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>rVQsrZR4</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -769,25 +799,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
+          <t xml:space="preserve">touchan r 
   usa </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6LuGZiZI</t>
+          <t>zoZ995af</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6BusaLE3</t>
+          <t>jBBpU7Y0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
+          <t>dYUosgsB</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -795,25 +825,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">bazakos f 
-  usa </t>
+          <t xml:space="preserve">lauziere p 
+  can </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UL7r7duf</t>
+          <t>022mBmSn</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GzULyFoh</t>
+          <t>6gpXy3vi</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
+          <t>U3Cs29yR</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -821,25 +851,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">demianchuk s 
+          <t xml:space="preserve">freemon j 
   usa </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>WSL0wFD4</t>
+          <t>GzULyFoh</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UFWZoX9L</t>
+          <t>K4FYmLD9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
+          <t>vcKjtDdH</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -847,25 +877,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
+          <t xml:space="preserve">marrufo j 
   usa </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>WWvwigh8</t>
+          <t>zoZ995af</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t>6BusaLE3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
+          <t>Me49cTqr</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -873,25 +903,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">villarreal a 
+          <t xml:space="preserve">mendoza r 
   usa </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>WSL0wFD4</t>
+          <t>xA45kovo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>86yPt28f</t>
+          <t>tOpyQa24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
+          <t>ImJfuXBN</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -899,16 +929,224 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>0n3Ddmal</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SM4QZAZp</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>bFuhdIb3</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>URr9bfCo</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bazakos f 
+  usa </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>QDIbviRT</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">montero r 
+  cos </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>KIxd2dNg</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>rVnDcERi</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xhnHdYtb</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>GroLehd4</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YJuQfCBA</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t xml:space="preserve">demianchuk s 
   usa </t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>KtuTuMN0</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>UFWZoX9L</t>
         </is>

--- a/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -461,16 +456,10 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivas v 
-  usa </t>
+          <t>022mBmSn</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>022mBmSn</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
         <is>
           <t>63fk89be</t>
         </is>
@@ -487,16 +476,10 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
-  usa </t>
+          <t>roEEsq76</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>roEEsq76</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>l6eEjGlO</t>
         </is>
@@ -513,16 +496,10 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
+          <t>6LuGZiZI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>6LuGZiZI</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>dp6AQn9c</t>
         </is>
@@ -539,16 +516,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
+          <t>roEEsq76</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>roEEsq76</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>tOpyQa24</t>
         </is>
@@ -565,16 +536,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
+          <t>6LuGZiZI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>6LuGZiZI</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
         <is>
           <t>6BusaLE3</t>
         </is>
@@ -591,16 +556,10 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ford t 
-  usa </t>
+          <t>K4zRMgTN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>K4zRMgTN</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>WSL0wFD4</t>
         </is>
@@ -617,16 +576,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">allatin m 
-  usa </t>
+          <t>xA45kovo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
-        <is>
-          <t>xA45kovo</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>Sd7snoa0</t>
         </is>
@@ -643,16 +596,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">touchan r 
-  usa </t>
+          <t>6LuGZiZI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>6LuGZiZI</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
         <is>
           <t>jBBpU7Y0</t>
         </is>
@@ -669,16 +616,10 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">bazakos f 
-  usa </t>
+          <t>86yPt28f</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>86yPt28f</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
         <is>
           <t>GzULyFoh</t>
         </is>
@@ -695,16 +636,10 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">demianchuk s 
-  usa </t>
+          <t>GzULyFoh</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>GzULyFoh</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
         <is>
           <t>UFWZoX9L</t>
         </is>
@@ -721,16 +656,10 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
-  usa </t>
+          <t>WWvwigh8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
-        <is>
-          <t>WWvwigh8</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
         <is>
           <t>tOpyQa24</t>
         </is>
@@ -747,16 +676,10 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzales g 
-  usa </t>
+          <t>WSL0wFD4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
-        <is>
-          <t>WSL0wFD4</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
         <is>
           <t>UL7r7duf</t>
         </is>
@@ -773,16 +696,10 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">demianchuk s 
-  usa </t>
+          <t>Sd7snoa0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
-        <is>
-          <t>Sd7snoa0</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
         <is>
           <t>UFWZoX9L</t>
         </is>
@@ -799,356 +716,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">touchan r 
-  usa </t>
+          <t>zoZ995af</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>zoZ995af</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
           <t>jBBpU7Y0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dYUosgsB</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>022mBmSn</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>6gpXy3vi</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>U3Cs29yR</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">freemon j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>GzULyFoh</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>K4FYmLD9</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>vcKjtDdH</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>zoZ995af</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>6BusaLE3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Me49cTqr</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>xA45kovo</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>tOpyQa24</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>ImJfuXBN</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">da silva a 
-  usa </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>K4zRMgTN</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>l6eEjGlO</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>0n3Ddmal</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chapman a 
-  usa </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>86yPt28f</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>WWvwigh8</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SM4QZAZp</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">freemon j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>bFuhdIb3</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>K4FYmLD9</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>URr9bfCo</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bazakos f 
-  usa </t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>K4zRMgTN</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>nJ01AhXP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>QDIbviRT</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">montero r 
-  cos </t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>KIxd2dNg</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>lAVQ9RGh</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>rVnDcERi</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chapman a 
-  usa </t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>rXawJi8t</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>WWvwigh8</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>xhnHdYtb</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allatin m 
-  usa </t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>86yPt28f</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Sd7snoa0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>GroLehd4</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>EqKWmJfM</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2PIEeC7j</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YJuQfCBA</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">demianchuk s 
-  usa </t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>zoZ995af</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>UFWZoX9L</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>A3m1Vera</t>
+          <t>CAvUgWQG</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>022mBmSn</t>
+          <t>dp6AQn9c</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>63fk89be</t>
+          <t>6gpXy3vi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
+          <t>6XwYhjtN</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>roEEsq76</t>
+          <t>K4zRMgTN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>l6eEjGlO</t>
+          <t>K4FYmLD9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
+          <t>rBhIe7Ef</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +496,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>6LuGZiZI</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>dp6AQn9c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>I7sxhAeT</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,19 +516,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>roEEsq76</t>
+          <t>xA45kovo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t>022mBmSn</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>OlK4mU3p</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -541,14 +541,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6BusaLE3</t>
+          <t>6gpXy3vi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vquIRDsO</t>
+          <t>2uJ8nlJj</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -556,19 +556,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>K4zRMgTN</t>
+          <t>UL7r7duf</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>WSL0wFD4</t>
+          <t>Sd7snoa0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>jeCjBXei</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -576,19 +576,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>xA45kovo</t>
+          <t>rXawJi8t</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sd7snoa0</t>
+          <t>KtuTuMN0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>CA0a9BQ3</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -596,19 +596,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6LuGZiZI</t>
+          <t>63fk89be</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>jBBpU7Y0</t>
+          <t>roEEsq76</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
+          <t>UoBfAiBc</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -616,19 +616,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>86yPt28f</t>
+          <t>jBBpU7Y0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GzULyFoh</t>
+          <t>roEEsq76</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
+          <t>tdBLfRT0</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -636,19 +636,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GzULyFoh</t>
+          <t>jBBpU7Y0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>UFWZoX9L</t>
+          <t>zoZ995af</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
+          <t>QD438VuA</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -656,19 +656,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WWvwigh8</t>
+          <t>rXawJi8t</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t>2PIEeC7j</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
+          <t>zJAPgoq7</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -676,19 +676,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WSL0wFD4</t>
+          <t>EqKWmJfM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UL7r7duf</t>
+          <t>Sd7snoa0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
+          <t>Kz477keG</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -696,32 +696,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sd7snoa0</t>
+          <t>tOpyQa24</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>UFWZoX9L</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rVQsrZR4</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>zoZ995af</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>jBBpU7Y0</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/usa/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -448,127 +448,67 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CAvUgWQG</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>dp6AQn9c</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>6gpXy3vi</t>
-        </is>
-      </c>
+          <t>YuZ4CywD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6XwYhjtN</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>K4zRMgTN</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>K4FYmLD9</t>
-        </is>
-      </c>
+          <t>UuWb8pb0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rBhIe7Ef</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>GzULyFoh</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>6LuGZiZI</t>
-        </is>
-      </c>
+          <t>llHizuVJ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>I7sxhAeT</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>xA45kovo</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>022mBmSn</t>
-        </is>
-      </c>
+          <t>CWX8BehJ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OlK4mU3p</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>6LuGZiZI</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>6gpXy3vi</t>
-        </is>
-      </c>
+          <t>pK2NUIhs</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2uJ8nlJj</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>UL7r7duf</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Sd7snoa0</t>
-        </is>
-      </c>
+          <t>MFWf9Qrf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jeCjBXei</t>
+          <t>r5LQTx8m</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -576,19 +516,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rXawJi8t</t>
+          <t>WSL0wFD4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KtuTuMN0</t>
+          <t>WSL0wFD4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CA0a9BQ3</t>
+          <t>QTAVSdNg</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -596,19 +536,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>63fk89be</t>
+          <t>UL7r7duf</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>roEEsq76</t>
+          <t>GzULyFoh</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UoBfAiBc</t>
+          <t>4K9ZRGx0</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -616,19 +556,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jBBpU7Y0</t>
+          <t>lAVQ9RGh</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>roEEsq76</t>
+          <t>tOpyQa24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tdBLfRT0</t>
+          <t>YgEwRzh6</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -636,19 +576,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jBBpU7Y0</t>
+          <t>lAVQ9RGh</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>zoZ995af</t>
+          <t>KtuTuMN0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QD438VuA</t>
+          <t>CpDsQf7C</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -656,19 +596,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>rXawJi8t</t>
+          <t>bFuhdIb3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2PIEeC7j</t>
+          <t>UFWZoX9L</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>zJAPgoq7</t>
+          <t>SvGeZbpQ</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -676,19 +616,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EqKWmJfM</t>
+          <t>dp6AQn9c</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sd7snoa0</t>
+          <t>nJ01AhXP</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Kz477keG</t>
+          <t>f92nPEMI</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -696,12 +636,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>tOpyQa24</t>
+          <t>EqKWmJfM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>UFWZoX9L</t>
+          <t>WWvwigh8</t>
         </is>
       </c>
     </row>
